--- a/ashika-departments-import.xlsx
+++ b/ashika-departments-import.xlsx
@@ -449,7 +449,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,178 +465,230 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>head_email</t>
+          <t>main_module</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EQB</t>
+          <t>IB</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Equity Broking</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+          <t>Investment Banking</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Secretarial</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+          <t>Merchant Banking</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>INB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Wealth Management</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>Institutional Broking</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>institutional</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GFO</t>
+          <t>EQB</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Global Family office</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
+          <t>Equity Broking</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>institutional</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FO</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Family Office</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
+          <t>Wealth Management</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PCF</t>
+          <t>GFO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Private Credit Fund</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Global Family office</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PEF</t>
+          <t>FO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Private Equity Fund</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>Family Office</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>PCF</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Accounts - Main</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>Private Credit Fund</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>PEF</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bonds</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
+          <t>Private Equity Fund</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Merchant Banking</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
+          <t>Accounts - Main</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MGT</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+          <t>Bonds</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>IB</t>
+          <t>MGT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Investment Banking</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INB</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Institutional Broking</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>Secretarial</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -649,7 +701,11 @@
           <t>IT</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -662,7 +718,11 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -675,7 +735,11 @@
           <t>Operations</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -688,7 +752,11 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -701,7 +769,11 @@
           <t>Customer Support</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C19"/>
@@ -719,7 +791,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -742,7 +814,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>required, must be unique (same as manual create) — rows whose name already exists will be flagged</t>
+          <t>required, unique (existing names are flagged/skipped)</t>
         </is>
       </c>
     </row>
@@ -754,19 +826,19 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>optional, up to 12 characters</t>
+          <t>optional, up to 12 chars</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>head_email</t>
+          <t>main_module</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>optional — email of an existing user to make the department head</t>
+          <t>required — banking | institutional | internal (or full label: 'Investment Banking &amp; Merchant Banking', 'Institutional Business', 'Internal Work')</t>
         </is>
       </c>
     </row>
